--- a/data/processed/07_no_outliers_TOP3_contributors.xlsx
+++ b/data/processed/07_no_outliers_TOP3_contributors.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,19 +461,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>age_group</t>
+          <t>infra_consequences</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1502665009022351</v>
+        <v>-0.8270524558903019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1502665009022351</v>
+        <v>0.8270524558903019</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>living_area</t>
+          <t>climate_consequence_count</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1405548323156567</v>
+        <v>-0.7793232795058309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1405548323156567</v>
+        <v>0.7793232795058309</v>
       </c>
     </row>
     <row r="4">
@@ -503,24 +503,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>climate_event_count</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.136817988503846</v>
+        <v>-0.6094212262120364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.136817988503846</v>
+        <v>0.6094212262120364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -529,19 +529,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>age_group</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2307936901690208</v>
+        <v>0.1502665009022351</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2307936901690208</v>
+        <v>0.1502665009022351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -554,15 +554,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.170248945795638</v>
+        <v>0.1405548323156567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.170248945795638</v>
+        <v>0.1405548323156567</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -571,82 +571,82 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1637644766870281</v>
+        <v>0.136817988503846</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1637644766870281</v>
+        <v>0.136817988503846</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>age_group</t>
+          <t>health_consequences</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1448699528222755</v>
+        <v>1.903467469067202</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1448699528222755</v>
+        <v>1.903467469067202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>climate_consequence_count</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.0974472371242667</v>
+        <v>0.7213414082165756</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0974472371242667</v>
+        <v>0.7213414082165756</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>descriptive_num</t>
+          <t>clustering_12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>living_area</t>
+          <t>heat_experience</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09500499207345875</v>
+        <v>0.4737880643427335</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09500499207345875</v>
+        <v>0.4737880643427335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -659,15 +659,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1646439179498498</v>
+        <v>0.2307936901690208</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1646439179498498</v>
+        <v>0.2307936901690208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -676,34 +676,286 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>political_preference</t>
+          <t>living_area</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1035098269832223</v>
+        <v>-0.170248945795638</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1035098269832223</v>
+        <v>0.170248945795638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1637644766870281</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1637644766870281</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flood_experience</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.798905123487762</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.798905123487762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>climate_event_count</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.704382269411961</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.704382269411961</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>health_consequences</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5253570214625477</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5253570214625477</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>age_group</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1448699528222755</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1448699528222755</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.0974472371242667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0974472371242667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>living_area</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.09500499207345875</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.09500499207345875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>3</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>descriptive_num</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>infra_consequences</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.161768292250571</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.161768292250571</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flood_experience</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5559958256438227</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5559958256438227</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>clustering_12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>climate_consequence_count</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5430673959131715</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5430673959131715</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.1646439179498498</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1646439179498498</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>political_preference</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.1035098269832223</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1035098269832223</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>descriptive_num</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>kids</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D25" t="n">
         <v>-0.09246108805091295</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E25" t="n">
         <v>0.09246108805091295</v>
       </c>
     </row>
